--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_64924_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_64924_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc4a0b4cf89c84601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rde9b5982c1454759"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.5967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3895</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.1453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.0379</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0155</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.2124</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_64924_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_64924_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rde9b5982c1454759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R74f3fb84584e454d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4394</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2923</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4395</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.7687</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1153</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2649</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4893</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0155</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.1453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3397</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.3870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.5193</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8659</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.7687</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.0628</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.0379</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2399</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3946</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8659</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5916</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.1824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.1702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.5692</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4944</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.8934</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.2598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9656</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9631</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3946</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.6414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7163</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.8134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.2476</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -354,268 +1074,1153 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>     26.0632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.2124</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7361</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2399</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.3620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.9554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0455</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.2048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.0699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.4969</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3448</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.9208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7412</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.2374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.0903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.2597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.5117</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.2643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5916</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4669</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7412</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.5193</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3921</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4813</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4145</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4695</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8211</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1926</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.0206</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.2661</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.1152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.7188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.8460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.0979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.0929</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5916</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.8934</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7636</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.5941</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.9880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.6664</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.3672</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.6216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2923</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.7437</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>     26.0155</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>16/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.2124</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.1152</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.8409</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7361</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.2399</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7860</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.3620</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.9554</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.2648</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.6964</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.0455</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.1402</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.2048</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.5142</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.0699</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.4969</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.3448</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4669</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.3328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.8290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.2201</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1178</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -630,52 +2235,127 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.7412</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.6939</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.0903</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
+          <x:t>31/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.5055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.3122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3397</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9855</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.4944</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -690,637 +2370,1717 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>25/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.1427</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.2374</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.0903</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.4420</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.6939</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.2597</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.5117</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.2643</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5916</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.4669</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.7412</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.1875</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.5193</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.9880</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.3921</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.2124</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5666</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.4145</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.4695</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.8211</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.1926</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.0206</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.2661</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     22.9483</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.9906</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.1152</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.9905</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7735</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.7188</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.8460</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.0430</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.0979</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.0430</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.0929</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5916</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.8934</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7636</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.5941</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.1427</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.9880</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.6664</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.8409</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/06/2026</x:t>
+          <x:t>22/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.5168</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.0852</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4369</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.8109</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.0078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.2598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6012</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.2572</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.5213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.2221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.6511</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.4938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.5737</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.9177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.7956</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.8602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.3167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.5783</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.4063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.3014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.3813</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.3289</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.4184</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.7925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.4683</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.0195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.7950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.5406</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.1818</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.6429</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.6953</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.9792</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.1237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.6525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.3283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.8769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.6653</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.4159</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.3161</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.6627</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.5579</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.6627</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.2810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.8021</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.2235</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.3431</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.7095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.0260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.9634</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.1852</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.9634</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.8214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.1558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.7868</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.4077</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.6545</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.0535</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.9960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.8611</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.8611</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.7089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.5318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     71.5241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.6514</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.8336</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.7939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.7166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.8310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     73.8931</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.2646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     73.2448</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.2626</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.3349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     73.2198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.0427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.6041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.6789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.7384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.5165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.9506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.3918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.3867</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.3465</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.5831</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.7520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.1317</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.3343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.7613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.7415</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.7415</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.6066</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.4544</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     74.1425</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.8784</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.7964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.6245</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.4709</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.1550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.5091</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.2496</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.2037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.9823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.3164</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.7950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.6647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.5471</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.2402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/02/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.9971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.3045</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.6588</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/01/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/01/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1335,2046 +4095,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>12/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.6216</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.2923</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.7437</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.0155</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.4170</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.4669</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.2175</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.3328</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.8290</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.2201</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.1178</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     23.9208</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.4394</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.4643</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.3122</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.3397</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.7610</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.2175</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.9855</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     24.4944</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.5392</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.5168</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.0852</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.4369</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.8109</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.0078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.2598</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.6012</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.2572</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     33.5213</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.0501</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     33.2221</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.6511</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     34.4938</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.5737</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     34.9177</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     33.7956</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     37.8602</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     35.3167</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     40.5783</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.4063</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     41.3014</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.3813</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     40.3289</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     44.4184</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     44.7925</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     44.4683</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     44.0195</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     43.7950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     45.5406</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.1818</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     44.6429</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     43.6953</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     49.9792</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     52.1237</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     50.6525</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     50.3283</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     50.8769</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     45.6653</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     45.4159</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     45.3161</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     46.6627</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     48.5579</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     46.6627</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     49.2810</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     50.8021</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     52.2235</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     54.3431</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.7095</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.0260</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     65.9634</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     67.1852</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/04/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     65.9634</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     62.8214</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     59.1558</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     56.7868</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     58.4077</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     59.6545</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     60.0535</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     62.9960</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.8611</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.8611</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     67.7089</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     68.5318</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     71.5241</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     70.6514</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     67.8336</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     63.7939</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     64.7166</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     68.8310</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     73.8931</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     75.2646</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     73.2448</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.2626</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     67.3349</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     73.2198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     74.0427</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     69.6041</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     69.6789</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     75.7384</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     74.5165</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     70.9506</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     74.3918</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/03/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     76.3867</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     82.3465</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     87.5831</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     99.7520</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     88.1317</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     77.3343</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.7613</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     64.7415</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     64.7415</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     68.6066</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     69.4544</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     74.1425</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     69.8784</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     62.7964</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.6245</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     40.1045</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.1550</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.9030</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     28.9081</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.3519</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.2496</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     36.2037</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     38.9823</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     41.3164</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     43.7950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     55.6647</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     62.5471</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     65.2402</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/02/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     42.9971</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.5290</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     29.7726</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/01/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     25.3672</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>27/01/2026</x:t>
         </x:is>
       </x:c>
@@ -3414,7 +4134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.4601</x:v>
+        <x:v>     33.8954</x:v>
       </x:c>
     </x:row>
     <x:row>
